--- a/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Бердянск 130133082.xlsx
+++ b/в бланки заводов/Останкино ЗПФ/ostankino_zpf/NV/чистый бланк/Заказ ЗПФ Новое время Бердянск 130133082.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино ЗПФ\ostankino_zpf\NV\чистый бланк\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961E8A1F-4729-4678-A5D1-2221B1A1A1FA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94EDCC2D-B5CE-4285-9055-5C3476659F7B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
     <definedName name="кол_во_инд.__упак_к">Бланк!$AC$3:$AC$448</definedName>
     <definedName name="номин.вес_нетто__кг">Бланк!$W$3:$W$448</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -592,7 +592,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -735,27 +735,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="2" fontId="7" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -765,20 +744,32 @@
     <xf numFmtId="1" fontId="9" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="1" fontId="8" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -788,7 +779,7 @@
     <xf numFmtId="164" fontId="15" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -798,7 +789,47 @@
     <cellStyle name="Обычный 13" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Обычный 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1258,14 +1289,14 @@
       <c r="D1" s="39">
         <v>130133082</v>
       </c>
-      <c r="E1" s="65" t="s">
+      <c r="E1" s="62" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="66"/>
-      <c r="G1" s="66"/>
-      <c r="H1" s="66"/>
-      <c r="I1" s="66"/>
-      <c r="J1" s="67"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="J1" s="64"/>
       <c r="K1" s="26">
         <v>130133079</v>
       </c>
@@ -1298,22 +1329,22 @@
       <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="58">
+      <c r="D3" s="51">
         <v>46209</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="58">
+      <c r="F3" s="51">
         <f>D3+3</f>
         <v>46212</v>
       </c>
-      <c r="G3" s="68" t="s">
+      <c r="G3" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="66"/>
-      <c r="J3" s="67"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="64"/>
       <c r="K3" s="26">
         <v>130133081</v>
       </c>
@@ -1487,7 +1518,7 @@
       <c r="A13" s="56">
         <v>6149</v>
       </c>
-      <c r="B13" s="51" t="s">
+      <c r="B13" s="49" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="47" t="s">
@@ -1516,7 +1547,7 @@
       <c r="A14" s="56">
         <v>6819</v>
       </c>
-      <c r="B14" s="51" t="s">
+      <c r="B14" s="49" t="s">
         <v>26</v>
       </c>
       <c r="C14" s="47" t="s">
@@ -1545,7 +1576,7 @@
       <c r="A15" s="56">
         <v>6202</v>
       </c>
-      <c r="B15" s="51" t="s">
+      <c r="B15" s="49" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="47" t="s">
@@ -1574,7 +1605,7 @@
       <c r="A16" s="56">
         <v>6148</v>
       </c>
-      <c r="B16" s="51" t="s">
+      <c r="B16" s="49" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="47" t="s">
@@ -1603,7 +1634,7 @@
       <c r="A17" s="56">
         <v>6209</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B17" s="49" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="47" t="s">
@@ -1632,13 +1663,13 @@
       <c r="A18" s="56">
         <v>6168</v>
       </c>
-      <c r="B18" s="51" t="s">
+      <c r="B18" s="49" t="s">
         <v>30</v>
       </c>
       <c r="C18" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="52">
+      <c r="D18" s="48">
         <v>1002131156168</v>
       </c>
       <c r="E18" s="23"/>
@@ -1655,19 +1686,19 @@
       <c r="I18" s="14">
         <v>120</v>
       </c>
-      <c r="J18" s="55"/>
+      <c r="J18" s="28"/>
     </row>
     <row r="19" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="56">
         <v>5579</v>
       </c>
-      <c r="B19" s="51" t="s">
+      <c r="B19" s="49" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D19" s="52">
+      <c r="D19" s="48">
         <v>1002134275579</v>
       </c>
       <c r="E19" s="23"/>
@@ -1684,26 +1715,26 @@
       <c r="I19" s="14">
         <v>120</v>
       </c>
-      <c r="J19" s="55"/>
+      <c r="J19" s="28"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="50">
+      <c r="A20" s="57">
         <v>5754</v>
       </c>
-      <c r="B20" s="53" t="s">
+      <c r="B20" s="58" t="s">
         <v>32</v>
       </c>
       <c r="C20" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="52">
+      <c r="D20" s="48">
         <v>1002131155754</v>
       </c>
       <c r="E20" s="23"/>
       <c r="F20" s="22">
         <v>4.5</v>
       </c>
-      <c r="G20" s="54">
+      <c r="G20" s="59">
         <f>E20</f>
         <v>0</v>
       </c>
@@ -1713,10 +1744,10 @@
       <c r="I20" s="14">
         <v>120</v>
       </c>
-      <c r="J20" s="55"/>
+      <c r="J20" s="28"/>
     </row>
     <row r="21" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="50">
+      <c r="A21" s="57">
         <v>5755</v>
       </c>
       <c r="B21" s="49" t="s">
@@ -1732,7 +1763,7 @@
       <c r="F21" s="22">
         <v>4.5</v>
       </c>
-      <c r="G21" s="54">
+      <c r="G21" s="59">
         <f>E21</f>
         <v>0</v>
       </c>
@@ -1745,46 +1776,46 @@
       <c r="J21" s="28"/>
     </row>
     <row r="22" spans="1:10" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="59"/>
-      <c r="B22" s="69" t="s">
+      <c r="A22" s="52"/>
+      <c r="B22" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="69"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="66"/>
     </row>
     <row r="23" spans="1:10" ht="15.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="60">
         <v>7216</v>
       </c>
-      <c r="B23" s="61" t="s">
+      <c r="B23" s="53" t="s">
         <v>46</v>
       </c>
       <c r="C23" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="62">
+      <c r="D23" s="61">
         <v>1002116437216</v>
       </c>
-      <c r="E23" s="63"/>
+      <c r="E23" s="54"/>
       <c r="F23" s="22">
         <v>0.7</v>
       </c>
-      <c r="G23" s="54">
-        <f>E23</f>
+      <c r="G23" s="59">
+        <f>E23*F23</f>
         <v>0</v>
       </c>
       <c r="H23" s="14"/>
-      <c r="I23" s="64"/>
-      <c r="J23" s="64"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
     </row>
     <row r="24" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="57"/>
+      <c r="A24" s="50"/>
       <c r="B24" s="44" t="s">
         <v>21</v>
       </c>
@@ -1796,7 +1827,7 @@
       </c>
       <c r="F24" s="16"/>
       <c r="G24" s="16">
-        <f>SUM(G11:G23)</f>
+        <f>SUM(G12:G23)</f>
         <v>0</v>
       </c>
       <c r="H24" s="16"/>
